--- a/artfynd/A 45582-2022 artfynd.xlsx
+++ b/artfynd/A 45582-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45582-2022 artfynd.xlsx
+++ b/artfynd/A 45582-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>800688</v>
+        <v>358679</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grangytterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscopannaria ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.M.Jørg.) P.M.Jørg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583585.9489896599</v>
+        <v>583119</v>
       </c>
       <c r="R2" t="n">
-        <v>7302030.029777306</v>
+        <v>7301930</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,24 +743,14 @@
           <t>2005-09-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-09-08</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på silikatstenshäll tillsammans med lunglav och Physconia detersa, näringsgynnat, rävgödslad?,</t>
+          <t>påverkat av rikare sippervatten, block nedanför brant, mycket skrovellav på klippan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +764,22 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>i lövdominerad skog i sydostsluttning</t>
+          <t>i sydostbrant med björkgranskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På sluttande häll skyddat under överluta på block</t>
+          <t>Sparsam på sydvänd lodyta på silikatstensblock</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>2831</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,12 +800,7 @@
         <v>381540</v>
       </c>
       <c r="B3" t="n">
-        <v>78513</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583119.0607139858</v>
+        <v>583119</v>
       </c>
       <c r="R3" t="n">
-        <v>7301929.909770572</v>
+        <v>7301930</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,19 +865,9 @@
           <t>2005-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -939,15 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1993528</v>
+        <v>800688</v>
       </c>
       <c r="B4" t="n">
-        <v>78568</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583585.9489896599</v>
+        <v>583586</v>
       </c>
       <c r="R4" t="n">
-        <v>7302030.029777306</v>
+        <v>7302030</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,24 +987,14 @@
           <t>2005-09-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-09-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på silikatstenshäll tillsammans med Physconia detersa och skrovellav, näringsgynnat, rävgödslad?,</t>
+          <t>på silikatstenshäll tillsammans med lunglav och Physconia detersa, näringsgynnat, rävgödslad?,</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1066,37 +1031,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>358679</v>
+        <v>1993528</v>
       </c>
       <c r="B5" t="n">
-        <v>78510</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1150</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grangytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscopannaria ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.M.Jørg.) P.M.Jørg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583119.0607139858</v>
+        <v>583586</v>
       </c>
       <c r="R5" t="n">
-        <v>7301929.909770572</v>
+        <v>7302030</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1139,24 +1099,14 @@
           <t>2005-09-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-09-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>påverkat av rikare sippervatten, block nedanför brant, mycket skrovellav på klippan</t>
+          <t>på silikatstenshäll tillsammans med Physconia detersa och skrovellav, näringsgynnat, rävgödslad?,</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,22 +1120,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>i sydostbrant med björkgranskog</t>
+          <t>i lövdominerad skog i sydostsluttning</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Sparsam på sydvänd lodyta på silikatstensblock</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>2831</t>
+          <t>På sluttande häll skyddat under överluta på block</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 45582-2022 artfynd.xlsx
+++ b/artfynd/A 45582-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/358679</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/381540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/800688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,8 +1160,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1993528</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>